--- a/artfynd/A 40019-2024 artfynd.xlsx
+++ b/artfynd/A 40019-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121151190</v>
+        <v>121151191</v>
       </c>
       <c r="B2" t="n">
-        <v>91957</v>
+        <v>91967</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -719,13 +719,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>767989</v>
+        <v>767849</v>
       </c>
       <c r="R2" t="n">
-        <v>7485986</v>
+        <v>7486106</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -749,12 +749,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-09-13</t>
+          <t>2024-09-05</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-09-13</t>
+          <t>2024-09-05</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121151191</v>
+        <v>121151190</v>
       </c>
       <c r="B3" t="n">
-        <v>91957</v>
+        <v>91967</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -821,7 +821,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -830,13 +830,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>767849</v>
+        <v>767989</v>
       </c>
       <c r="R3" t="n">
-        <v>7486106</v>
+        <v>7485986</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -860,12 +860,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-09-05</t>
+          <t>2024-09-13</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-09-05</t>
+          <t>2024-09-13</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">

--- a/artfynd/A 40019-2024 artfynd.xlsx
+++ b/artfynd/A 40019-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121151191</v>
       </c>
       <c r="B2" t="n">
-        <v>91967</v>
+        <v>91979</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>121151190</v>
       </c>
       <c r="B3" t="n">
-        <v>91967</v>
+        <v>91979</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 40019-2024 artfynd.xlsx
+++ b/artfynd/A 40019-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121151191</v>
+        <v>121151190</v>
       </c>
       <c r="B2" t="n">
-        <v>91979</v>
+        <v>91980</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -719,13 +719,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>767849</v>
+        <v>767989</v>
       </c>
       <c r="R2" t="n">
-        <v>7486106</v>
+        <v>7485986</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -749,12 +749,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-09-05</t>
+          <t>2024-09-13</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-09-05</t>
+          <t>2024-09-13</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121151190</v>
+        <v>121151191</v>
       </c>
       <c r="B3" t="n">
-        <v>91979</v>
+        <v>91980</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -821,7 +821,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -830,13 +830,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>767989</v>
+        <v>767849</v>
       </c>
       <c r="R3" t="n">
-        <v>7485986</v>
+        <v>7486106</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -860,12 +860,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-09-13</t>
+          <t>2024-09-05</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-09-13</t>
+          <t>2024-09-05</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">

--- a/artfynd/A 40019-2024 artfynd.xlsx
+++ b/artfynd/A 40019-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121151190</v>
       </c>
       <c r="B2" t="n">
-        <v>91980</v>
+        <v>91983</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>121151191</v>
       </c>
       <c r="B3" t="n">
-        <v>91980</v>
+        <v>91983</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 40019-2024 artfynd.xlsx
+++ b/artfynd/A 40019-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121151190</v>
+        <v>121151191</v>
       </c>
       <c r="B2" t="n">
         <v>91983</v>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -719,13 +719,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>767989</v>
+        <v>767849</v>
       </c>
       <c r="R2" t="n">
-        <v>7485986</v>
+        <v>7486106</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -749,12 +749,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-09-13</t>
+          <t>2024-09-05</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-09-13</t>
+          <t>2024-09-05</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -786,7 +786,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121151191</v>
+        <v>121151190</v>
       </c>
       <c r="B3" t="n">
         <v>91983</v>
@@ -821,7 +821,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -830,13 +830,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>767849</v>
+        <v>767989</v>
       </c>
       <c r="R3" t="n">
-        <v>7486106</v>
+        <v>7485986</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -860,12 +860,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-09-05</t>
+          <t>2024-09-13</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-09-05</t>
+          <t>2024-09-13</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
